--- a/themes/statements.xlsx
+++ b/themes/statements.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -470,181 +470,81 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    NotAuthorized: Для заказа справки по закрытому продукту напишите в чат приложения «Уралсиб Онлайн» или его [веб-версии](https://online.uralsib.ru/)</t>
+          <t xml:space="preserve">    NotAuthorized: Для заказа справки по цессионому кредиту напишите в чат приложения «Уралсиб Онлайн» или его [веб-версии](https://online.uralsib.ru/)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">    NotAuthorized: Для заказа справки по закрытому продукту напишите в чат приложения «Уралсиб Онлайн» или его [веб-версии](https://online.uralsib.ru/).</t>
+          <t xml:space="preserve">    NotAuthorized: Для заказа справки по цессионному кредиту напишите в чат приложения «Уралсиб Онлайн» или его [веб-версии](https://online.uralsib.ru/)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>добавлена точка в конце предложения</t>
+          <t>опечатка «цессионому» → «цессионному» (пропущена буква «н», ср. со строкой 11)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>50</v>
+        <v>126</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">    NotAuthorized: Для заказа справки по цессионому кредиту напишите в чат приложения «Уралсиб Онлайн» или его [веб-версии](https://online.uralsib.ru/)</t>
+          <t xml:space="preserve">        - Дальнейшую информацию по справкам и выпискам предоставит оператор – переключаю вас.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">    NotAuthorized: Для заказа справки по цессионному кредиту напишите в чат приложения «Уралсиб Онлайн» или его [веб-версии](https://online.uralsib.ru/).</t>
+          <t xml:space="preserve">        - Дальнейшую информацию по справкам и выпискам предоставит оператор — переключаю вас.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>опечатка «цессионому» → «цессионному» (пропущена буква «н», ср. со строкой 11); добавлена точка в конце предложения</t>
+          <t>эн-дефис (–) заменён на тире (—)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    NotAuthorized: Для уточнения статуса заказа справки напишите в чат приложения «Уралсиб Онлайн» или его [веб-версии](https://online.uralsib.ru/)</t>
+          <t xml:space="preserve">    Answer: Укажите, какой документ хотите получить</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    NotAuthorized: Для уточнения статуса заказа справки напишите в чат приложения «Уралсиб Онлайн» или его [веб-версии](https://online.uralsib.ru/).</t>
+          <t xml:space="preserve">    Answer: Укажите, какой документ хотите получить?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>добавлена точка в конце предложения</t>
+          <t>добавлен вопросительный знак в конце предложения</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124</v>
+        <v>164</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">    NotAuthorized: Для уточнения информации о справках напишите в чат приложения «Уралсиб Онлайн» или его [веб-версии](https://online.uralsib.ru/)</t>
+          <t xml:space="preserve">    Final: Квитанцию можно выгрузить в PDF формате, отправить письмом на электронную почту и распечатать чек.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">    NotAuthorized: Для уточнения информации о справках напишите в чат приложения «Уралсиб Онлайн» или его [веб-версии](https://online.uralsib.ru/).</t>
+          <t xml:space="preserve">    Final: Квитанцию можно выгрузить в PDF-формате, отправить письмом на электронную почту и распечатать чек.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>добавлена точка в конце предложения</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>126</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        - Дальнейшую информацию по справкам и выпискам предоставит оператор – переключаю вас.</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        - Дальнейшую информацию по справкам и выпискам предоставит оператор — переключаю вас.</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>эн-дефис (–) заменён на тире (—)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>130</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Answer: Укажите, какой документ хотите получить</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Answer: Укажите, какой документ хотите получить?</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>добавлен вопросительный знак в конце предложения</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>164</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Final: Квитанцию можно выгрузить в PDF формате, отправить письмом на электронную почту и распечатать чек.</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Final: Квитанцию можно выгрузить в PDF-формате, отправить письмом на электронную почту и распечатать чек.</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
           <t>составное слово «PDF-формате» пишется через дефис</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>170</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">          1. Операция ещё обрабатывается (значок часов рядом с ней не исчез)</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">          1. Операция ещё обрабатывается (значок часов рядом с ней не исчез).</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>добавлена точка в конце предложения</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>172</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">          2. Это зачисление денег на карту</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">          2. Это зачисление денег на карту.</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>добавлена точка в конце предложения</t>
         </is>
       </c>
     </row>
